--- a/data/trans_dic/IP31KM02_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM02_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>58,99%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>42,52; 64,16</t>
+          <t>51,73; 73,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49,71; 72,76</t>
+          <t>43,63; 65,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49,98; 66,43</t>
+          <t>51,31; 67,19</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>66,14%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>59,3; 71,5</t>
+          <t>59,34; 71,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>58,37; 69,83</t>
+          <t>61,08; 72,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60,26; 69,41</t>
+          <t>62,11; 70,51</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>62,88%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>53,73; 66,95</t>
+          <t>57,22; 69,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>56,11; 69,18</t>
+          <t>54,87; 68,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57,19; 66,48</t>
+          <t>58,6; 67,22</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>53,98%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33,57; 55,31</t>
+          <t>46,8; 59,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43,33; 57,17</t>
+          <t>48,74; 60,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41,66; 54,67</t>
+          <t>49,26; 58,21</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>59,67%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>48,81; 60,54</t>
+          <t>56,0; 63,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>54,2; 61,97</t>
+          <t>56,07; 62,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53,5; 60,05</t>
+          <t>57,05; 62,33</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>44</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25015</t>
+          <t>23679</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27859</t>
+          <t>23580</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52873</t>
+          <t>47259</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19770; 29830</t>
+          <t>19364; 27347</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22510; 32951</t>
+          <t>18621; 28078</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45870; 60965</t>
+          <t>41106; 53831</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>174</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>104392</t>
+          <t>102867</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>117133</t>
+          <t>97248</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>221525</t>
+          <t>200116</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>94460; 113905</t>
+          <t>93186; 111633</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>106200; 127065</t>
+          <t>88876; 105664</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>205629; 236879</t>
+          <t>187919; 213328</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>144</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>105593</t>
+          <t>127016</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>133071</t>
+          <t>108668</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>238664</t>
+          <t>235684</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>92988; 115880</t>
+          <t>114505; 138618</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>119225; 146995</t>
+          <t>95849; 118845</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>220505; 256304</t>
+          <t>219620; 251949</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>182</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>131321</t>
+          <t>157272</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>155558</t>
+          <t>138322</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>286879</t>
+          <t>295594</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>92084; 151703</t>
+          <t>136749; 174198</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>132170; 174364</t>
+          <t>124463; 153888</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>241302; 316671</t>
+          <t>269706; 318738</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>544</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>568</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>366321</t>
+          <t>410834</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>433620</t>
+          <t>367819</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>799941</t>
+          <t>778653</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>318794; 395379</t>
+          <t>384652; 434676</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>403613; 461505</t>
+          <t>346615; 386977</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>747858; 839350</t>
+          <t>744514; 813442</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM02_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM02_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que toman una 2ª pieza de fruta todos los días (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>63,25%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>55,25%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>58,99%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>51,73; 73,05</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>43,63; 65,79</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>51,31; 67,19</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>65,5%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>66,83%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>66,14%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>59,34; 71,08</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>61,08; 72,61</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>62,11; 70,51</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>63,47%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>62,21%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>62,88%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>57,22; 69,27</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>54,87; 68,04</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>58,6; 67,22</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>53,82%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>54,17%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>53,98%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>46,8; 59,61</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>48,74; 60,27</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>49,26; 58,21</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>59,82%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>59,5%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>59,67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>56,0; 63,29</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>56,07; 62,6</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>57,05; 62,33</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.6325327984742647</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.5524810074671029</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.5898861977609497</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>23679</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>23580</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>47259</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.5172705330383635</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.4362862179647963</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.5130762039530197</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>19364; 27347</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>18621; 28078</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>41106; 53831</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.7305124643237053</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.657850490130346</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.6719079703097314</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.6550295045780251</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.6682916315399571</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.6614079935185442</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>102867</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>97248</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>200116</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.5933801961203186</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.6107547193920423</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.6210973662046821</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>93186; 111633</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>88876; 105664</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>187919; 213328</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.7108469518750044</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.7261255294265612</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.7050770549826724</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>295</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.6346800997878284</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.6221262149191019</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.6288294414538023</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>127016</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>108668</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>235684</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.572164994912939</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.5487398570056751</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.5859688011754755</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>114505; 138618</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>95849; 118845</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>219620; 251949</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.6926555585384219</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.6803900727659786</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.6722267572413182</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>373</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.5381957609998629</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.5417243504773797</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.5398412122779684</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>157272</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>138322</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>295594</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.4679635800731282</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.4874464393716671</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.4925612374639704</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>136749; 174198</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>124463; 153888</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>269706; 318738</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.5961165520420919</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.6026871216479565</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.5821076319894627</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>568</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>544</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1112</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.5981650478493215</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.5949764411916042</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.5966545698772431</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>410834</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>367819</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>778653</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.5600451767137267</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.5606765139598505</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.5704954957137994</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>384652; 434676</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>346615; 386977</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>744514; 813442</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.6328778798302169</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.6259662197340933</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.6233121690315467</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que toman una 2ª pieza de fruta todos los días (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>23679</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>23580</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>47259</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>19364</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>18621</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>41106</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>27347</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>28078</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>53831</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>176</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>174</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>102867</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>97248</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>200116</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>93186</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>88876</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>187919</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>111633</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>105664</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>213328</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>151</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>144</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>127016</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>108668</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>235684</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>114505</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>95849</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>219620</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>138618</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>118845</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>251949</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>191</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>182</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>157272</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>138322</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>295594</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>136749</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>124463</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>269706</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>174198</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>153888</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>318738</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>568</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>544</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>410834</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>367819</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>778653</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>384652</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>346615</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>744514</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>434676</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>386977</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>813442</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>